--- a/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WBD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>WBD</t>
   </si>
@@ -656,342 +656,354 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8717000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8893000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9460000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9045000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9812000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8979000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10027000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9623000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9713000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9958000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10284000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9979000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10358000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10700000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11008000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9823000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9827000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3159000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3187000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3150000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3062000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2792000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2886000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2561000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2541000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4621000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4601000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5119000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4528000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5967000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5096000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5457000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5036000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6204000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6058000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6000000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5118000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6636000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6589000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6954000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4718000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6123000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1232000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1065000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1527000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1054000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>969000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1089000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1002000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>804000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4096000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4292000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4341000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4517000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3845000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3883000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4570000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4587000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3509000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3900000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4284000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4861000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3722000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4111000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4054000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5105000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3704000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1927000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2122000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1623000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2008000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1823000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1797000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1559000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1737000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1019,8 +1031,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1096,8 +1109,11 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1173,162 +1189,171 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>314000</v>
+      </c>
+      <c r="E14" s="3">
         <v>3260000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>355000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>178000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2835000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>263000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>489000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>174000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8832000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>118000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>495000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>215000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>308000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1198000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2430000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1535000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>9000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>15000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>8000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>18000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>150000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>70000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1159000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1226000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1315000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1375000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1447000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1547000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1643000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1762000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1744000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1888000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2024000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1989000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1914000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2058000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2169000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2233000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2266000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>525000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>539000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>341000</v>
       </c>
       <c r="W15" s="3">
         <v>341000</v>
       </c>
       <c r="X15" s="3">
+        <v>341000</v>
+      </c>
+      <c r="Y15" s="3">
         <v>361000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>358000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>341000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>334000</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1353,162 +1378,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8272000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8129000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8762000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8255000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9871000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8758000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9385000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9121000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10365000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10118000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10425000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9385000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11127000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10988000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12902000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12013000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13466000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2806000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2679000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2827000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2284000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2399000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2406000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2046000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1895000</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>445000</v>
+      </c>
+      <c r="E18" s="3">
         <v>764000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>698000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>790000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-59000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>221000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>642000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>502000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-652000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-160000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-141000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>594000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-769000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-288000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1894000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2190000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3639000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>353000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>508000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>323000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>778000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>393000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>480000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>515000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>646000</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1536,393 +1568,409 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-78000</v>
+      </c>
+      <c r="E20" s="3">
         <v>62000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>62000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-88000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-14000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>135000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>26000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>92000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>103000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-25000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>124000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>18000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>111000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-89000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-106000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-94000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>476000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-171000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>69000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>99000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>67000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>109000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-25000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1682000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1928000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1813000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2103000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1476000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1782000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2150000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2238000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1000000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1625000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1908000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2459000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1127000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1659000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4270000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3878000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3649000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2323000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1642000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1952000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1991000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1564000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1785000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1594000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1613000</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>514000</v>
+      </c>
+      <c r="E22" s="3">
         <v>584000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>587000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>570000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>469000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>470000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>412000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>529000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>522000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>498000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>540000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>550000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>518000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>576000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>558000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>555000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>511000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>153000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>154000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>159000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>157000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>163000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>173000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>171000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>172000</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-271000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3120000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-408000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>27000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2454000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-434000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-356000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-178000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10035000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-819000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-613000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-532000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1480000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1238000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2541000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2851000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4244000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>676000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>183000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>233000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>720000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>297000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>416000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>319000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>456000</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-433000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-214000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-161000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>170000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>866000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>15000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>284000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-319000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>136000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-221000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-125000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-260000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-178000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-462000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-566000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-836000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>201000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>92000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>36000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>106000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>98000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>156000</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1998,162 +2046,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2906000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-247000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-143000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1588000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-449000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-640000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>141000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10028000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-955000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-392000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-407000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1220000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1060000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2079000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2285000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3408000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>475000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>91000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>197000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>718000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>191000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>318000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>330000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2916000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-251000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-148000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1580000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-453000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-493000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>135000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9986000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-970000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-400000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-417000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1240000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1069000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2101000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2308000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3418000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>407000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>48000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>120000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>515000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>106000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>205000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>223000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2229,8 +2286,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2306,8 +2366,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2383,8 +2446,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2460,162 +2526,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-62000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-62000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>88000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>14000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-135000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-26000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-92000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-103000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>25000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-124000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-18000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-111000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>89000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>106000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>94000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-476000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>171000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-69000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-99000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-67000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-109000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>25000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2916000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-252000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-148000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1580000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-453000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-494000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>135000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9986000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-966000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-400000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-417000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1240000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1069000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2101000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2308000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3418000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>407000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>48000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>120000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>515000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>106000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>205000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>223000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2691,167 +2766,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2916000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-252000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-148000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1580000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-453000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-494000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>135000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9986000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-966000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-400000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-417000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1240000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1069000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2101000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2308000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3418000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>407000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>48000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>120000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>515000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>106000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>205000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>223000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2879,8 +2963,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2908,130 +2993,134 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3369000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3264000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4566000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4294000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4888000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3868000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5312000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3336000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3613000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2976000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3780000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2383000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3027000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2594000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3731000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2422000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2575000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4162000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3905000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3116000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2834000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2008000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2091000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1893000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1683000</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>32000</v>
+        <v>42000</v>
       </c>
       <c r="E42" s="3">
         <v>17000</v>
       </c>
       <c r="F42" s="3">
+        <v>17000</v>
+      </c>
+      <c r="G42" s="3">
         <v>32000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>29000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>36000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>18000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>68000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>93000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>24000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>83000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>72000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>40000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3062,85 +3151,91 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3148000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3357000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4136000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3316000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3210000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2818000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3887000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3498000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3599000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3643000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4532000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3683000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3485000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3558000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6380000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6669000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7049000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2426000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2446000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2462000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2657000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2476000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2537000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2444000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2473000</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3183,8 +3278,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3216,393 +3311,411 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1724000</v>
+        <v>1888000</v>
       </c>
       <c r="E45" s="3">
+        <v>1739000</v>
+      </c>
+      <c r="F45" s="3">
         <v>4483000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1876000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2251000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1909000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4758000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2140000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2659000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2742000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2906000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2755000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3607000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3374000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3888000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3581000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5825000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>585000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>913000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1078000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1237000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1381000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1502000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1141000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>561000</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12539000</v>
+      </c>
+      <c r="E46" s="3">
         <v>11741000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13206000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13062000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13611000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12782000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14078000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12505000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13430000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13902000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14218000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12831000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13773000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13727000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13999000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12672000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15449000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7173000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7264000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6656000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6728000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5865000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6130000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5478000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4717000</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1165000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1232000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1250000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1276000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1262000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1293000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1331000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1474000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1517000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1437000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1470000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1443000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1491000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1499000</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3" t="s">
+      <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U47" s="3">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V47" s="3">
         <v>543000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>545000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>559000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>522000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>507000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>536000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6652000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6642000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8082000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6517000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6413000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6211000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7214000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6158000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6043000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5937000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7730000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5810000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5473000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5325000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8490000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8365000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8515000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1328000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1336000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1310000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1239000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1189000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1206000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1125000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1088000</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>71028000</v>
+      </c>
+      <c r="E49" s="3">
         <v>71989000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>74163000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>73813000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>74662000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>75600000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>78314000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>79675000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>80907000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>91978000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>95784000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>97055000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>100888000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>103370000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>106072000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>109482000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>113117000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>22611000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>23061000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>23429000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>23694000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23765000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>24149000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>24194000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>24618000</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3678,8 +3791,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3755,85 +3871,91 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5864000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6233000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2762000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5851000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5779000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5793000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3010000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6521000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6132000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6565000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2858000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6610000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6993000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6663000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5440000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5530000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5159000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2687000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2223000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2378000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2352000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2284000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2095000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2105000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2136000</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3909,85 +4031,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>97248000</v>
+      </c>
+      <c r="E54" s="3">
         <v>97837000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>100085000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>100519000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>101727000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>101679000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>104560000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>106333000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>108029000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>119819000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>122757000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>123749000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>128618000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>130584000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>134001000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>136049000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>142240000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33799000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>34427000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34318000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>34572000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33625000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34087000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33438000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33089000</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4015,8 +4143,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4044,85 +4173,89 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1060000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1110000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1093000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1083000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1074000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1008000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1055000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1120000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1151000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1245000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1260000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1329000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1689000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1123000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1454000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1534000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1397000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>521000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>412000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2361000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2174000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2128000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>397000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>403000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>367000</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4130,384 +4263,399 @@
         <v>1493000</v>
       </c>
       <c r="E58" s="3">
+        <v>1493000</v>
+      </c>
+      <c r="F58" s="3">
         <v>573000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>139000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>221000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2779000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3162000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3043000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3669000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3430000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2186000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1302000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3001000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3496000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>447000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1338000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1175000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>794000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>397000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>349000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>585000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>351000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>392000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>336000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>339000</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1514000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1592000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2310000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1649000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1527000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1600000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2213000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1788000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2022000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2312000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1924000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2431000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2020000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2099000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13116000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11804000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11864000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2247000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2650000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>625000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>806000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>663000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2293000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2017000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1870000</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16143000</v>
+      </c>
+      <c r="E60" s="3">
         <v>16115000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12500000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12163000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13040000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15286000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15810000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15695000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17768000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16956000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15332000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14588000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>16906000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16380000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15017000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14676000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14436000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3562000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3459000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3335000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3565000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3142000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3082000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2756000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2576000</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30530000</v>
+      </c>
+      <c r="E61" s="3">
         <v>30973000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>36188000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>33382000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>34411000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>34647000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>39844000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>37166000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>37293000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>39155000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>45104000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>43504000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>44289000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>45435000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>48820000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>48799000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>51594000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13605000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14617000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14436000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14462000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14675000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>15253000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14981000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14944000</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10659000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10809000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7263000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10734000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10205000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9651000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6529000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9769000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9532000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9892000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6689000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10275000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10527000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10337000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>21497000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>22494000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23263000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3070000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2955000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3149000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3237000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3233000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3369000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3661000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3769000</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4583,8 +4731,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4660,8 +4811,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4737,85 +4891,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>63253000</v>
+      </c>
+      <c r="E66" s="3">
         <v>64130000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>62919000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>63214000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>64381000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>66508000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>69622000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>70159000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>72614000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>74525000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>76285000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>77607000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>81833000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>82742000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>86906000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>87532000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>90857000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>21830000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>22828000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>22707000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23034000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>22810000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23623000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23351000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23222000</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4843,8 +5003,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4920,8 +5081,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4997,8 +5161,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5074,8 +5241,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5151,85 +5321,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14279000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-14428000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-11512000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11260000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11112000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-12692000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-12239000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-11745000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11880000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1894000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-928000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-526000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-105000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1133000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2205000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4306000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6614000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>10033000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>9580000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9522000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>9360000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8682000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8543000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8278000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7980000</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5305,8 +5481,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5382,8 +5561,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5459,85 +5641,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>32838000</v>
+      </c>
+      <c r="E76" s="3">
         <v>32578000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35919000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>36018000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>36049000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>33836000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>34037000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>35100000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>34345000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>44151000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45226000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>44774000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45452000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>46496000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>47095000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>48517000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>51383000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11969000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11599000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11611000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11538000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10815000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10464000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10087000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9867000</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5613,167 +5801,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2916000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-252000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-148000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1580000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-453000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-494000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>135000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9986000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-966000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-400000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-417000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1240000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1069000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2101000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2308000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3418000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>407000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>48000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>120000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>515000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>106000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>205000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>223000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5801,85 +5998,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1447000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1547000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1643000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1762000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1744000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1888000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2024000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1989000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1914000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2058000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2169000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2233000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2266000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>525000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6253000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6174000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7382000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1494000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1305000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1560000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1114000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1104000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1196000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1104000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>985000</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5955,8 +6156,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6032,8 +6236,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6109,8 +6316,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6186,8 +6396,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6263,85 +6476,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>848000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-208000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1804000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>979000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>983000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>553000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2715000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>847000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1228000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>585000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3578000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2516000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2014000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-631000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2846000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>124000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1011000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>323000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>884000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>811000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>834000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>269000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>553000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>860000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>991000</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6369,85 +6588,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-276000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-268000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-421000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-278000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-281000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-251000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-286000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-215000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-252000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-195000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-268000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-457000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-292000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-299000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-364000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-316000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-222000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-85000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-106000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-77000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-90000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-112000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-73000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-112000</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6523,8 +6746,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6600,85 +6826,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-282000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-418000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-330000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-236000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-195000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>6000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-218000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>70000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-207000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-234000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-458000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-310000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-257000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-218000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>862000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2351000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>529000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-26000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-226000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>40000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>156000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-153000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-396000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-84000</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6706,8 +6938,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6750,8 +6983,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6783,8 +7016,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6860,8 +7096,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6937,8 +7176,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7014,235 +7256,247 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-517000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-756000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1117000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1895000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-875000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1037000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1237000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1529000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2625000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1251000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-432000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1272000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2313000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3570000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-587000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-42000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-273000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-69000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-469000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-277000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-274000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-739000</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E101" s="3">
         <v>95000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-195000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>119000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-30000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-74000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>74000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-80000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-15000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>29000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>61000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-56000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-61000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>61000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-56000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-61000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-37000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-20000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>21000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-70000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>43000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>28000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1302000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>272000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-593000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>917000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1442000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1926000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-127000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>231000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-933000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1889000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-647000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>438000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1291000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1417000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1383000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-269000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>260000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>779000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>292000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>826000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-114000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>166000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>218000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>204000</v>
       </c>
     </row>
